--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.59093541702263</v>
+        <v>9.846027005266178</v>
       </c>
       <c r="D2" t="n">
-        <v>60.92622493978683</v>
+        <v>9.900511552715361</v>
       </c>
       <c r="E2" t="n">
-        <v>6.078487582321514</v>
+        <v>0.9877542321272462</v>
       </c>
       <c r="F2" t="n">
-        <v>6.171087280155048</v>
+        <v>1.002801683025196</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.92113976026879</v>
+        <v>9.574685211043679</v>
       </c>
       <c r="D3" t="n">
-        <v>59.20781348199839</v>
+        <v>9.621269690824739</v>
       </c>
       <c r="E3" t="n">
-        <v>6.078487582321514</v>
+        <v>0.9877542321272462</v>
       </c>
       <c r="F3" t="n">
-        <v>6.171087280155048</v>
+        <v>1.002801683025196</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.53249841429499</v>
+        <v>11.13653099232294</v>
       </c>
       <c r="D4" t="n">
-        <v>68.60787444906278</v>
+        <v>11.1487795979727</v>
       </c>
       <c r="E4" t="n">
-        <v>6.078487582321514</v>
+        <v>0.9877542321272462</v>
       </c>
       <c r="F4" t="n">
-        <v>6.171087280155048</v>
+        <v>1.002801683025196</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.31131510200707</v>
+        <v>8.338088704076149</v>
       </c>
       <c r="D5" t="n">
-        <v>51.30062749224579</v>
+        <v>8.336351967489941</v>
       </c>
       <c r="E5" t="n">
-        <v>6.078487582321514</v>
+        <v>0.9877542321272462</v>
       </c>
       <c r="F5" t="n">
-        <v>6.171087280155048</v>
+        <v>1.002801683025196</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.45098433289793</v>
+        <v>8.198284954095914</v>
       </c>
       <c r="D6" t="n">
-        <v>50.23361610007582</v>
+        <v>8.162962616262321</v>
       </c>
       <c r="E6" t="n">
-        <v>6.078487582321514</v>
+        <v>0.9877542321272462</v>
       </c>
       <c r="F6" t="n">
-        <v>6.171087280155048</v>
+        <v>1.002801683025196</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.29152489266541</v>
+        <v>9.634872795058131</v>
       </c>
       <c r="D7" t="n">
-        <v>59.01162751779451</v>
+        <v>9.589389471641608</v>
       </c>
       <c r="E7" t="n">
-        <v>6.078487582321514</v>
+        <v>0.9877542321272462</v>
       </c>
       <c r="F7" t="n">
-        <v>6.171087280155048</v>
+        <v>1.002801683025196</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
